--- a/result/eko_transactions.xlsx
+++ b/result/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9AF4C2-39CE-4278-90C3-7D1903054EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D0E1B2-C2B4-42FD-AE68-0CF732978CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="30" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аграрен Университет Пловдив" sheetId="1" r:id="rId1"/>
@@ -1468,6 +1468,15 @@
     <t>08:39:49</t>
   </si>
   <si>
+    <t>ТХ4680АТ</t>
+  </si>
+  <si>
+    <t>78970151027720864</t>
+  </si>
+  <si>
+    <t>11:42:25</t>
+  </si>
+  <si>
     <t>ТХ3500РХ</t>
   </si>
   <si>
@@ -2831,15 +2840,6 @@
   </si>
   <si>
     <t>15:27:11</t>
-  </si>
-  <si>
-    <t>ТХ4680АТ</t>
-  </si>
-  <si>
-    <t>78970151027720864</t>
-  </si>
-  <si>
-    <t>11:42:25</t>
   </si>
   <si>
     <t>17:05:36</t>
@@ -3107,12 +3107,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3127,8 +3133,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8457,7 +8464,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8695,10 +8702,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
         <v>470</v>
@@ -8707,22 +8714,22 @@
         <v>471</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="J8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="K8">
-        <v>23.04</v>
+        <v>175.5</v>
       </c>
       <c r="L8" t="s">
         <v>472</v>
       </c>
       <c r="M8">
-        <v>293920</v>
+        <v>195014</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8730,7 +8737,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
         <v>473</v>
@@ -8742,51 +8749,51 @@
         <v>34</v>
       </c>
       <c r="F9">
-        <v>21.654</v>
+        <v>18</v>
       </c>
       <c r="J9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="K9">
-        <v>27.5</v>
+        <v>23.04</v>
       </c>
       <c r="L9" t="s">
         <v>475</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>293920</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
         <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D10" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>21.654</v>
       </c>
       <c r="J10">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="K10">
-        <v>48.47</v>
+        <v>27.5</v>
       </c>
       <c r="L10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M10">
-        <v>294360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8797,28 +8804,28 @@
         <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D11" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J11">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="K11">
-        <v>60.84</v>
+        <v>48.47</v>
       </c>
       <c r="L11" t="s">
         <v>479</v>
       </c>
       <c r="M11">
-        <v>175626</v>
+        <v>294360</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8835,22 +8842,22 @@
         <v>481</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J12">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="K12">
-        <v>31.44</v>
+        <v>60.84</v>
       </c>
       <c r="L12" t="s">
         <v>482</v>
       </c>
       <c r="M12">
-        <v>17510</v>
+        <v>175626</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8867,22 +8874,22 @@
         <v>484</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>35.006999999999998</v>
+        <v>24</v>
       </c>
       <c r="J13">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="K13">
-        <v>49.01</v>
+        <v>31.44</v>
       </c>
       <c r="L13" t="s">
         <v>485</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>17510</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8902,24 +8909,24 @@
         <v>17</v>
       </c>
       <c r="F14">
-        <v>47.2</v>
+        <v>35.006999999999998</v>
       </c>
       <c r="J14">
         <v>1.4</v>
       </c>
       <c r="K14">
-        <v>66.08</v>
+        <v>49.01</v>
       </c>
       <c r="L14" t="s">
         <v>488</v>
       </c>
       <c r="M14">
-        <v>36027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>217</v>
@@ -8931,27 +8938,27 @@
         <v>490</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>47.2</v>
       </c>
       <c r="J15">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="K15">
-        <v>20.96</v>
+        <v>66.08</v>
       </c>
       <c r="L15" t="s">
         <v>491</v>
       </c>
       <c r="M15">
-        <v>74300</v>
+        <v>36027</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>217</v>
@@ -8963,22 +8970,22 @@
         <v>493</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="J16">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="K16">
-        <v>83.52</v>
+        <v>20.96</v>
       </c>
       <c r="L16" t="s">
         <v>494</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8989,25 +8996,25 @@
         <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D17" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
       </c>
       <c r="F17">
-        <v>42.014000000000003</v>
+        <v>58</v>
       </c>
       <c r="J17">
         <v>1.44</v>
       </c>
       <c r="K17">
-        <v>60.5</v>
+        <v>83.52</v>
       </c>
       <c r="L17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -9021,28 +9028,28 @@
         <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D18" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
       <c r="F18">
-        <v>54</v>
+        <v>42.014000000000003</v>
       </c>
       <c r="J18">
         <v>1.44</v>
       </c>
       <c r="K18">
-        <v>77.760000000000005</v>
+        <v>60.5</v>
       </c>
       <c r="L18" t="s">
         <v>498</v>
       </c>
       <c r="M18">
-        <v>276902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9062,83 +9069,83 @@
         <v>17</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J19">
         <v>1.44</v>
       </c>
       <c r="K19">
-        <v>48.96</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="L19" t="s">
         <v>501</v>
       </c>
       <c r="M19">
-        <v>250700</v>
+        <v>276902</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
         <v>217</v>
       </c>
       <c r="C20" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20">
         <v>34</v>
       </c>
-      <c r="F20">
-        <v>28</v>
-      </c>
       <c r="J20">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="K20">
-        <v>36.96</v>
+        <v>48.96</v>
       </c>
       <c r="L20" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M20">
-        <v>294720</v>
+        <v>250700</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>217</v>
       </c>
       <c r="C21" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
       <c r="D21" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>38.24</v>
+        <v>28</v>
       </c>
       <c r="J21">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="K21">
-        <v>55.83</v>
+        <v>36.96</v>
       </c>
       <c r="L21" t="s">
         <v>505</v>
       </c>
       <c r="M21">
-        <v>283500</v>
+        <v>294720</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -9155,21 +9162,53 @@
         <v>507</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F22">
-        <v>38.540999999999997</v>
+        <v>38.24</v>
       </c>
       <c r="J22">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="K22">
-        <v>52.03</v>
+        <v>55.83</v>
       </c>
       <c r="L22" t="s">
         <v>508</v>
       </c>
       <c r="M22">
+        <v>283500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" t="s">
+        <v>509</v>
+      </c>
+      <c r="D23" t="s">
+        <v>510</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23">
+        <v>38.540999999999997</v>
+      </c>
+      <c r="J23">
+        <v>1.35</v>
+      </c>
+      <c r="K23">
+        <v>52.03</v>
+      </c>
+      <c r="L23" t="s">
+        <v>511</v>
+      </c>
+      <c r="M23">
         <v>227885</v>
       </c>
     </row>
@@ -9232,10 +9271,10 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -9250,7 +9289,7 @@
         <v>59.64</v>
       </c>
       <c r="L2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -9264,10 +9303,10 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -9282,7 +9321,7 @@
         <v>77.489999999999995</v>
       </c>
       <c r="L3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -9296,10 +9335,10 @@
         <v>326</v>
       </c>
       <c r="C4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -9314,7 +9353,7 @@
         <v>95.73</v>
       </c>
       <c r="L4" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -9328,10 +9367,10 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -9346,7 +9385,7 @@
         <v>75.87</v>
       </c>
       <c r="L5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -9411,10 +9450,10 @@
         <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -9435,7 +9474,7 @@
         <v>52.84</v>
       </c>
       <c r="L2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -9449,10 +9488,10 @@
         <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -9473,7 +9512,7 @@
         <v>40.92</v>
       </c>
       <c r="L3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -9487,10 +9526,10 @@
         <v>335</v>
       </c>
       <c r="C4" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D4" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -9511,7 +9550,7 @@
         <v>51.73</v>
       </c>
       <c r="L4" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -9576,10 +9615,10 @@
         <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -9600,7 +9639,7 @@
         <v>131</v>
       </c>
       <c r="L2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -9614,10 +9653,10 @@
         <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -9638,7 +9677,7 @@
         <v>26.54</v>
       </c>
       <c r="L3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -9652,10 +9691,10 @@
         <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D4" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -9676,7 +9715,7 @@
         <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -9690,10 +9729,10 @@
         <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -9714,7 +9753,7 @@
         <v>50</v>
       </c>
       <c r="L5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -9728,10 +9767,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -9752,7 +9791,7 @@
         <v>89.66</v>
       </c>
       <c r="L6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -9766,10 +9805,10 @@
         <v>288</v>
       </c>
       <c r="C7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D7" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -9790,7 +9829,7 @@
         <v>53.01</v>
       </c>
       <c r="L7" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -9804,10 +9843,10 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -9828,7 +9867,7 @@
         <v>145.27000000000001</v>
       </c>
       <c r="L8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -9842,10 +9881,10 @@
         <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D9" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -9866,7 +9905,7 @@
         <v>141</v>
       </c>
       <c r="L9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -9880,10 +9919,10 @@
         <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D10" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -9904,7 +9943,7 @@
         <v>118.03</v>
       </c>
       <c r="L10" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -9918,10 +9957,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D11" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -9942,7 +9981,7 @@
         <v>136.05000000000001</v>
       </c>
       <c r="L11" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -9956,10 +9995,10 @@
         <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D12" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -9980,7 +10019,7 @@
         <v>155.97999999999999</v>
       </c>
       <c r="L12" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -9994,10 +10033,10 @@
         <v>288</v>
       </c>
       <c r="C13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D13" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -10018,7 +10057,7 @@
         <v>56.06</v>
       </c>
       <c r="L13" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -10032,10 +10071,10 @@
         <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D14" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -10056,7 +10095,7 @@
         <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -10070,10 +10109,10 @@
         <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D15" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -10094,7 +10133,7 @@
         <v>145</v>
       </c>
       <c r="L15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -10108,10 +10147,10 @@
         <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D16" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -10132,7 +10171,7 @@
         <v>60.01</v>
       </c>
       <c r="L16" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -10146,10 +10185,10 @@
         <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D17" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -10170,7 +10209,7 @@
         <v>116.46</v>
       </c>
       <c r="L17" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -10184,10 +10223,10 @@
         <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D18" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -10208,7 +10247,7 @@
         <v>55.32</v>
       </c>
       <c r="L18" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -10222,10 +10261,10 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D19" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -10246,7 +10285,7 @@
         <v>196.38</v>
       </c>
       <c r="L19" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -10260,10 +10299,10 @@
         <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D20" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -10284,7 +10323,7 @@
         <v>47.41</v>
       </c>
       <c r="L20" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -10349,10 +10388,10 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -10373,7 +10412,7 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -10438,10 +10477,10 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -10462,7 +10501,7 @@
         <v>77.75</v>
       </c>
       <c r="L2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -10476,10 +10515,10 @@
         <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D3" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -10500,7 +10539,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="L3" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -10514,10 +10553,10 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -10538,7 +10577,7 @@
         <v>101.48</v>
       </c>
       <c r="L4" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -10692,10 +10731,10 @@
         <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E2" t="s">
         <v>152</v>
@@ -10716,7 +10755,7 @@
         <v>51.09</v>
       </c>
       <c r="L2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -10730,10 +10769,10 @@
         <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -10754,7 +10793,7 @@
         <v>32.130000000000003</v>
       </c>
       <c r="L3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -10768,10 +10807,10 @@
         <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D4" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E4" t="s">
         <v>152</v>
@@ -10792,7 +10831,7 @@
         <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -10803,13 +10842,13 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -10830,7 +10869,7 @@
         <v>38.369999999999997</v>
       </c>
       <c r="L5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -10844,10 +10883,10 @@
         <v>438</v>
       </c>
       <c r="C6" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D6" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
@@ -10868,7 +10907,7 @@
         <v>30.57</v>
       </c>
       <c r="L6" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -10882,10 +10921,10 @@
         <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D7" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
@@ -10906,7 +10945,7 @@
         <v>24.87</v>
       </c>
       <c r="L7" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -10920,10 +10959,10 @@
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -10944,7 +10983,7 @@
         <v>74.53</v>
       </c>
       <c r="L8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -10958,10 +10997,10 @@
         <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D9" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E9" t="s">
         <v>34</v>
@@ -10982,7 +11021,7 @@
         <v>39.299999999999997</v>
       </c>
       <c r="L9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -11047,10 +11086,10 @@
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -11071,7 +11110,7 @@
         <v>49.88</v>
       </c>
       <c r="L2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -11085,13 +11124,13 @@
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F3">
         <v>52.119</v>
@@ -11103,7 +11142,7 @@
         <v>30.75</v>
       </c>
       <c r="L3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M3">
         <v>1058</v>
@@ -11117,13 +11156,13 @@
         <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D4" t="s">
+        <v>593</v>
+      </c>
+      <c r="E4" t="s">
         <v>590</v>
-      </c>
-      <c r="E4" t="s">
-        <v>587</v>
       </c>
       <c r="F4">
         <v>37.627000000000002</v>
@@ -11135,7 +11174,7 @@
         <v>22.2</v>
       </c>
       <c r="L4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -11149,13 +11188,13 @@
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F5">
         <v>44.466999999999999</v>
@@ -11167,7 +11206,7 @@
         <v>26.68</v>
       </c>
       <c r="L5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -11181,13 +11220,13 @@
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E6" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F6">
         <v>29.75</v>
@@ -11199,7 +11238,7 @@
         <v>17.850000000000001</v>
       </c>
       <c r="L6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -11213,10 +11252,10 @@
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D7" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -11237,7 +11276,7 @@
         <v>56.43</v>
       </c>
       <c r="L7" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M7">
         <v>203263</v>
@@ -11251,13 +11290,13 @@
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F8">
         <v>46.871000000000002</v>
@@ -11269,7 +11308,7 @@
         <v>29.06</v>
       </c>
       <c r="L8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -11283,10 +11322,10 @@
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D9" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -11307,7 +11346,7 @@
         <v>54.87</v>
       </c>
       <c r="L9" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -11321,13 +11360,13 @@
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D10" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E10" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F10">
         <v>44.854999999999997</v>
@@ -11339,7 +11378,7 @@
         <v>27.81</v>
       </c>
       <c r="L10" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -11353,10 +11392,10 @@
         <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D11" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -11377,7 +11416,7 @@
         <v>62.03</v>
       </c>
       <c r="L11" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -11392,20 +11431,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -11456,10 +11481,10 @@
         <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -11480,7 +11505,7 @@
         <v>80.37</v>
       </c>
       <c r="L2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -11494,10 +11519,10 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D3" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -11518,7 +11543,7 @@
         <v>248.9</v>
       </c>
       <c r="L3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M3">
         <v>152744</v>
@@ -11532,10 +11557,10 @@
         <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D4" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -11556,7 +11581,7 @@
         <v>301.52999999999997</v>
       </c>
       <c r="L4" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M4">
         <v>94246</v>
@@ -11570,10 +11595,10 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -11594,7 +11619,7 @@
         <v>50.34</v>
       </c>
       <c r="L5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -11608,10 +11633,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -11632,7 +11657,7 @@
         <v>82.2</v>
       </c>
       <c r="L6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -11646,10 +11671,10 @@
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D7" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -11670,7 +11695,7 @@
         <v>91.7</v>
       </c>
       <c r="L7" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M7">
         <v>229183</v>
@@ -11684,10 +11709,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -11708,7 +11733,7 @@
         <v>279.3</v>
       </c>
       <c r="L8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="M8">
         <v>186160</v>
@@ -11722,10 +11747,10 @@
         <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D9" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -11746,7 +11771,7 @@
         <v>432.28</v>
       </c>
       <c r="L9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -11760,10 +11785,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D10" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -11784,7 +11809,7 @@
         <v>133</v>
       </c>
       <c r="L10" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -11798,10 +11823,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D11" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -11822,7 +11847,7 @@
         <v>133</v>
       </c>
       <c r="L11" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M11">
         <v>168084</v>
@@ -11836,10 +11861,10 @@
         <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D12" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -11860,7 +11885,7 @@
         <v>356.47</v>
       </c>
       <c r="L12" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -11874,10 +11899,10 @@
         <v>357</v>
       </c>
       <c r="C13" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D13" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -11898,7 +11923,7 @@
         <v>81.13</v>
       </c>
       <c r="L13" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M13">
         <v>241812</v>
@@ -11912,10 +11937,10 @@
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D14" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -11936,7 +11961,7 @@
         <v>226.1</v>
       </c>
       <c r="L14" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M14">
         <v>227750</v>
@@ -11947,13 +11972,13 @@
         <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C15" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D15" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E15" t="s">
         <v>34</v>
@@ -11974,7 +11999,7 @@
         <v>49.56</v>
       </c>
       <c r="L15" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -11988,10 +12013,10 @@
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D16" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -12012,7 +12037,7 @@
         <v>48.41</v>
       </c>
       <c r="L16" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -12026,10 +12051,10 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D17" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E17" t="s">
         <v>152</v>
@@ -12050,7 +12075,7 @@
         <v>68.010000000000005</v>
       </c>
       <c r="L17" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -12064,10 +12089,10 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D18" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -12088,7 +12113,7 @@
         <v>405</v>
       </c>
       <c r="L18" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -12102,10 +12127,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D19" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -12126,7 +12151,7 @@
         <v>54</v>
       </c>
       <c r="L19" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -12140,10 +12165,10 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D20" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -12164,7 +12189,7 @@
         <v>40.5</v>
       </c>
       <c r="L20" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -12178,10 +12203,10 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D21" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -12202,7 +12227,7 @@
         <v>298.19</v>
       </c>
       <c r="L21" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="M21">
         <v>186266</v>
@@ -12216,10 +12241,10 @@
         <v>335</v>
       </c>
       <c r="C22" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D22" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E22" t="s">
         <v>152</v>
@@ -12240,7 +12265,7 @@
         <v>34.72</v>
       </c>
       <c r="L22" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -12254,10 +12279,10 @@
         <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D23" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E23" t="s">
         <v>126</v>
@@ -12278,7 +12303,7 @@
         <v>64.02</v>
       </c>
       <c r="L23" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -12292,10 +12317,10 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D24" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -12316,7 +12341,7 @@
         <v>320.91000000000003</v>
       </c>
       <c r="L24" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -12330,10 +12355,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D25" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -12354,7 +12379,7 @@
         <v>306.45999999999998</v>
       </c>
       <c r="L25" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -12368,10 +12393,10 @@
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D26" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -12392,7 +12417,7 @@
         <v>60.86</v>
       </c>
       <c r="L26" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -12406,10 +12431,10 @@
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D27" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -12430,7 +12455,7 @@
         <v>165.6</v>
       </c>
       <c r="L27" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -12444,10 +12469,10 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D28" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -12468,7 +12493,7 @@
         <v>241.51</v>
       </c>
       <c r="L28" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M28">
         <v>152884</v>
@@ -12482,10 +12507,10 @@
         <v>326</v>
       </c>
       <c r="C29" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D29" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -12506,7 +12531,7 @@
         <v>80</v>
       </c>
       <c r="L29" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -12520,10 +12545,10 @@
         <v>249</v>
       </c>
       <c r="C30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D30" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E30" t="s">
         <v>152</v>
@@ -12544,7 +12569,7 @@
         <v>49.93</v>
       </c>
       <c r="L30" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -12558,10 +12583,10 @@
         <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D31" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -12582,7 +12607,7 @@
         <v>85.8</v>
       </c>
       <c r="L31" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -12596,10 +12621,10 @@
         <v>288</v>
       </c>
       <c r="C32" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D32" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -12620,7 +12645,7 @@
         <v>334.62</v>
       </c>
       <c r="L32" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -12634,10 +12659,10 @@
         <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D33" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -12658,7 +12683,7 @@
         <v>343.2</v>
       </c>
       <c r="L33" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="M33">
         <v>186580</v>
@@ -12672,10 +12697,10 @@
         <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D34" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -12696,7 +12721,7 @@
         <v>113.43</v>
       </c>
       <c r="L34" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -12707,13 +12732,13 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C35" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D35" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E35" t="s">
         <v>34</v>
@@ -12734,7 +12759,7 @@
         <v>56.13</v>
       </c>
       <c r="L35" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -12748,10 +12773,10 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D36" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -12772,7 +12797,7 @@
         <v>290</v>
       </c>
       <c r="L36" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -12786,10 +12811,10 @@
         <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D37" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -12810,7 +12835,7 @@
         <v>217.5</v>
       </c>
       <c r="L37" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -12824,10 +12849,10 @@
         <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D38" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -12848,7 +12873,7 @@
         <v>43.5</v>
       </c>
       <c r="L38" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -12862,10 +12887,10 @@
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D39" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -12886,7 +12911,7 @@
         <v>320.14</v>
       </c>
       <c r="L39" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M39">
         <v>168696</v>
@@ -12900,10 +12925,10 @@
         <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D40" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -12924,7 +12949,7 @@
         <v>330.6</v>
       </c>
       <c r="L40" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -12938,10 +12963,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D41" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
@@ -12962,7 +12987,7 @@
         <v>543.92999999999995</v>
       </c>
       <c r="L41" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -12976,10 +13001,10 @@
         <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D42" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -13000,7 +13025,7 @@
         <v>81.069999999999993</v>
       </c>
       <c r="L42" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -13014,10 +13039,10 @@
         <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D43" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E43" t="s">
         <v>34</v>
@@ -13038,7 +13063,7 @@
         <v>57.89</v>
       </c>
       <c r="L43" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -13052,10 +13077,10 @@
         <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D44" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -13076,7 +13101,7 @@
         <v>261.12</v>
       </c>
       <c r="L44" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="M44">
         <v>228044</v>
@@ -13090,10 +13115,10 @@
         <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D45" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E45" t="s">
         <v>34</v>
@@ -13114,7 +13139,7 @@
         <v>46.24</v>
       </c>
       <c r="L45" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="M45">
         <v>320946</v>
@@ -13128,10 +13153,10 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D46" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -13152,7 +13177,7 @@
         <v>70.03</v>
       </c>
       <c r="L46" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -13166,10 +13191,10 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D47" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -13190,7 +13215,7 @@
         <v>335.8</v>
       </c>
       <c r="L47" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="M47">
         <v>95210</v>
@@ -13204,10 +13229,10 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D48" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -13228,7 +13253,7 @@
         <v>356.11</v>
       </c>
       <c r="L48" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -13242,10 +13267,10 @@
         <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D49" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -13266,7 +13291,7 @@
         <v>225</v>
       </c>
       <c r="L49" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -13280,10 +13305,10 @@
         <v>45</v>
       </c>
       <c r="C50" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D50" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -13304,7 +13329,7 @@
         <v>255</v>
       </c>
       <c r="L50" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="M50">
         <v>153022</v>
@@ -13318,10 +13343,10 @@
         <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D51" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E51" t="s">
         <v>152</v>
@@ -13342,7 +13367,7 @@
         <v>83.48</v>
       </c>
       <c r="L51" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -13407,10 +13432,10 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -13425,7 +13450,7 @@
         <v>68.040000000000006</v>
       </c>
       <c r="L2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -13439,10 +13464,10 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D3" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -13457,7 +13482,7 @@
         <v>77.97</v>
       </c>
       <c r="L3" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -13471,10 +13496,10 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D4" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -13489,7 +13514,7 @@
         <v>101.57</v>
       </c>
       <c r="L4" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -13503,10 +13528,10 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -13521,7 +13546,7 @@
         <v>7.05</v>
       </c>
       <c r="L5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="M5">
         <v>417712</v>
@@ -13535,10 +13560,10 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D6" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -13553,7 +13578,7 @@
         <v>80.98</v>
       </c>
       <c r="L6" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="M6">
         <v>418164</v>
@@ -13567,10 +13592,10 @@
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D7" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -13591,7 +13616,7 @@
         <v>46.91</v>
       </c>
       <c r="L7" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="M7">
         <v>418365</v>
@@ -13605,10 +13630,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D8" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -13629,7 +13654,7 @@
         <v>75.78</v>
       </c>
       <c r="L8" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M8">
         <v>418765</v>
@@ -13643,10 +13668,10 @@
         <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -13667,7 +13692,7 @@
         <v>89.15</v>
       </c>
       <c r="L9" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M9">
         <v>419227</v>
@@ -13732,10 +13757,10 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -13756,7 +13781,7 @@
         <v>91.69</v>
       </c>
       <c r="L2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="M2">
         <v>670010</v>
@@ -13770,10 +13795,10 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D3" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -13794,7 +13819,7 @@
         <v>96.43</v>
       </c>
       <c r="L3" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M3">
         <v>178835</v>
@@ -13808,10 +13833,10 @@
         <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D4" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -13832,7 +13857,7 @@
         <v>82</v>
       </c>
       <c r="L4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="M4">
         <v>194080</v>
@@ -13846,10 +13871,10 @@
         <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -13870,7 +13895,7 @@
         <v>49.5</v>
       </c>
       <c r="L5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="M5">
         <v>410214</v>
@@ -13884,10 +13909,10 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D6" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -13908,7 +13933,7 @@
         <v>79.2</v>
       </c>
       <c r="L6" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -13922,10 +13947,10 @@
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D7" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -13946,7 +13971,7 @@
         <v>59.13</v>
       </c>
       <c r="L7" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="M7">
         <v>230247</v>
@@ -13960,10 +13985,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D8" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -13984,7 +14009,7 @@
         <v>111.02</v>
       </c>
       <c r="L8" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="M8">
         <v>670651</v>
@@ -13998,10 +14023,10 @@
         <v>406</v>
       </c>
       <c r="C9" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -14022,7 +14047,7 @@
         <v>74.290000000000006</v>
       </c>
       <c r="L9" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="M9">
         <v>194645</v>
@@ -14036,10 +14061,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D10" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -14060,7 +14085,7 @@
         <v>81.44</v>
       </c>
       <c r="L10" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="M10">
         <v>226108</v>
@@ -14074,10 +14099,10 @@
         <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D11" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -14098,7 +14123,7 @@
         <v>105.26</v>
       </c>
       <c r="L11" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -14109,13 +14134,13 @@
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C12" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D12" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -14136,7 +14161,7 @@
         <v>74.739999999999995</v>
       </c>
       <c r="L12" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="M12">
         <v>410521</v>
@@ -14150,10 +14175,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D13" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -14174,7 +14199,7 @@
         <v>86.28</v>
       </c>
       <c r="L13" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M13">
         <v>179389</v>
@@ -14188,10 +14213,10 @@
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D14" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -14212,7 +14237,7 @@
         <v>505.8</v>
       </c>
       <c r="L14" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="M14">
         <v>992395</v>
@@ -14226,10 +14251,10 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D15" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -14250,7 +14275,7 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M15">
         <v>671113</v>
@@ -14264,10 +14289,10 @@
         <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D16" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -14288,7 +14313,7 @@
         <v>78.510000000000005</v>
       </c>
       <c r="L16" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="M16">
         <v>195191</v>
@@ -14302,10 +14327,10 @@
         <v>357</v>
       </c>
       <c r="C17" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D17" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E17" t="s">
         <v>34</v>
@@ -14326,7 +14351,7 @@
         <v>38.92</v>
       </c>
       <c r="L17" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="M17">
         <v>126175</v>
@@ -14340,10 +14365,10 @@
         <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D18" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
@@ -14364,7 +14389,7 @@
         <v>39.71</v>
       </c>
       <c r="L18" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="M18">
         <v>234543</v>
@@ -14378,10 +14403,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D19" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -14402,7 +14427,7 @@
         <v>13.8</v>
       </c>
       <c r="L19" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -14416,10 +14441,10 @@
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D20" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -14440,7 +14465,7 @@
         <v>95.61</v>
       </c>
       <c r="L20" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="M20">
         <v>230802</v>
@@ -14454,10 +14479,10 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D21" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -14478,7 +14503,7 @@
         <v>82.71</v>
       </c>
       <c r="L21" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -14492,10 +14517,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D22" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -14516,7 +14541,7 @@
         <v>108.67</v>
       </c>
       <c r="L22" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="M22">
         <v>671531</v>
@@ -14527,13 +14552,13 @@
         <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C23" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D23" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -14554,7 +14579,7 @@
         <v>91.75</v>
       </c>
       <c r="L23" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="M23">
         <v>195848</v>
@@ -14565,13 +14590,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C24" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D24" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -14592,7 +14617,7 @@
         <v>454.55</v>
       </c>
       <c r="L24" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="M24">
         <v>993508</v>
@@ -14606,10 +14631,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D25" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -14630,7 +14655,7 @@
         <v>63.13</v>
       </c>
       <c r="L25" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="M25">
         <v>401080</v>
@@ -14644,10 +14669,10 @@
         <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D26" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -14668,7 +14693,7 @@
         <v>41.64</v>
       </c>
       <c r="L26" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -14682,10 +14707,10 @@
         <v>431</v>
       </c>
       <c r="C27" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D27" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -14706,7 +14731,7 @@
         <v>94.01</v>
       </c>
       <c r="L27" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="M27">
         <v>196490</v>
@@ -14720,10 +14745,10 @@
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D28" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -14744,7 +14769,7 @@
         <v>93.11</v>
       </c>
       <c r="L28" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="M28">
         <v>361742</v>
@@ -14755,13 +14780,13 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D29" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -14782,7 +14807,7 @@
         <v>89.14</v>
       </c>
       <c r="L29" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -14796,10 +14821,10 @@
         <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D30" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -14820,7 +14845,7 @@
         <v>84.8</v>
       </c>
       <c r="L30" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="M30">
         <v>179832</v>
@@ -14834,10 +14859,10 @@
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D31" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -14858,7 +14883,7 @@
         <v>91.28</v>
       </c>
       <c r="L31" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="M31">
         <v>231403</v>
@@ -14872,10 +14897,10 @@
         <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D32" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -14896,7 +14921,7 @@
         <v>97.8</v>
       </c>
       <c r="L32" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M32">
         <v>56192</v>
@@ -14910,10 +14935,10 @@
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D33" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -14934,7 +14959,7 @@
         <v>84.59</v>
       </c>
       <c r="L33" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="M33">
         <v>411132</v>
@@ -14948,10 +14973,10 @@
         <v>406</v>
       </c>
       <c r="C34" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D34" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -14972,7 +14997,7 @@
         <v>91.72</v>
       </c>
       <c r="L34" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="M34">
         <v>197165</v>
@@ -14986,10 +15011,10 @@
         <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D35" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -15010,7 +15035,7 @@
         <v>64.34</v>
       </c>
       <c r="L35" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="M35">
         <v>228275</v>
@@ -15024,10 +15049,10 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D36" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -15048,7 +15073,7 @@
         <v>59.68</v>
       </c>
       <c r="L36" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="M36">
         <v>231814</v>
@@ -15062,10 +15087,10 @@
         <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="D37" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -15086,7 +15111,7 @@
         <v>76.13</v>
       </c>
       <c r="L37" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="M37">
         <v>84897</v>
@@ -15097,13 +15122,13 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C38" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D38" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -15124,7 +15149,7 @@
         <v>97.34</v>
       </c>
       <c r="L38" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="M38">
         <v>190960</v>
@@ -15135,13 +15160,13 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C39" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D39" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E39" t="s">
         <v>34</v>
@@ -15162,7 +15187,7 @@
         <v>57.39</v>
       </c>
       <c r="L39" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="M39">
         <v>223845</v>
@@ -15173,16 +15198,16 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C40" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D40" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E40" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F40">
         <v>29.131</v>
@@ -15194,7 +15219,7 @@
         <v>17.77</v>
       </c>
       <c r="L40" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="M40">
         <v>223845</v>
@@ -15208,10 +15233,10 @@
         <v>349</v>
       </c>
       <c r="C41" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D41" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E41" t="s">
         <v>126</v>
@@ -15226,7 +15251,7 @@
         <v>70</v>
       </c>
       <c r="L41" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -15240,10 +15265,10 @@
         <v>217</v>
       </c>
       <c r="C42" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D42" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -15264,7 +15289,7 @@
         <v>97.78</v>
       </c>
       <c r="L42" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="M42">
         <v>180397</v>
@@ -15278,10 +15303,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D43" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -15302,7 +15327,7 @@
         <v>73.27</v>
       </c>
       <c r="L43" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="M43">
         <v>232260</v>
@@ -15316,10 +15341,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D44" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -15340,7 +15365,7 @@
         <v>103.2</v>
       </c>
       <c r="L44" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="M44">
         <v>22585</v>
@@ -15354,10 +15379,10 @@
         <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D45" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -15378,7 +15403,7 @@
         <v>74.290000000000006</v>
       </c>
       <c r="L45" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="M45">
         <v>411432</v>
@@ -15392,10 +15417,10 @@
         <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D46" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -15416,7 +15441,7 @@
         <v>90.11</v>
       </c>
       <c r="L46" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="M46">
         <v>226529</v>
@@ -15430,10 +15455,10 @@
         <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D47" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -15454,7 +15479,7 @@
         <v>26.36</v>
       </c>
       <c r="L47" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="M47">
         <v>361955</v>
@@ -15468,10 +15493,10 @@
         <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D48" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -15492,7 +15517,7 @@
         <v>87.83</v>
       </c>
       <c r="L48" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -15506,10 +15531,10 @@
         <v>406</v>
       </c>
       <c r="C49" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D49" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -15530,7 +15555,7 @@
         <v>101.3</v>
       </c>
       <c r="L49" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="M49">
         <v>191701</v>
@@ -15544,10 +15569,10 @@
         <v>406</v>
       </c>
       <c r="C50" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D50" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -15568,7 +15593,7 @@
         <v>59.91</v>
       </c>
       <c r="L50" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="M50">
         <v>192160</v>
@@ -15582,10 +15607,10 @@
         <v>406</v>
       </c>
       <c r="C51" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D51" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -15606,7 +15631,7 @@
         <v>19.5</v>
       </c>
       <c r="L51" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="M51">
         <v>197295</v>
@@ -15671,10 +15696,10 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -15695,7 +15720,7 @@
         <v>61.07</v>
       </c>
       <c r="L2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -15709,10 +15734,10 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D3" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -15733,7 +15758,7 @@
         <v>82.23</v>
       </c>
       <c r="L3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -15747,10 +15772,10 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D4" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -15771,7 +15796,7 @@
         <v>69.22</v>
       </c>
       <c r="L4" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -15836,10 +15861,10 @@
         <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D2" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E2" t="s">
         <v>126</v>
@@ -15860,7 +15885,7 @@
         <v>85.71</v>
       </c>
       <c r="L2" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -15874,10 +15899,10 @@
         <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D3" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -15898,7 +15923,7 @@
         <v>49.69</v>
       </c>
       <c r="L3" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -15912,10 +15937,10 @@
         <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D4" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -15936,7 +15961,7 @@
         <v>58.85</v>
       </c>
       <c r="L4" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M4">
         <v>349588</v>
@@ -15950,10 +15975,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E5" t="s">
         <v>152</v>
@@ -15974,7 +15999,7 @@
         <v>110.64</v>
       </c>
       <c r="L5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -15988,10 +16013,10 @@
         <v>196</v>
       </c>
       <c r="C6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D6" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -16012,7 +16037,7 @@
         <v>31.48</v>
       </c>
       <c r="L6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -16026,10 +16051,10 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D7" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -16050,7 +16075,7 @@
         <v>79.989999999999995</v>
       </c>
       <c r="L7" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="M7">
         <v>326660</v>
@@ -16064,10 +16089,10 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D8" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E8" t="s">
         <v>126</v>
@@ -16088,7 +16113,7 @@
         <v>91.81</v>
       </c>
       <c r="L8" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -16102,10 +16127,10 @@
         <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D9" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -16126,7 +16151,7 @@
         <v>181.86</v>
       </c>
       <c r="L9" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -16140,10 +16165,10 @@
         <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D10" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E10" t="s">
         <v>181</v>
@@ -16158,7 +16183,7 @@
         <v>8.43</v>
       </c>
       <c r="L10" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -16172,10 +16197,10 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D11" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -16196,7 +16221,7 @@
         <v>45.81</v>
       </c>
       <c r="L11" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="M11">
         <v>350060</v>
@@ -16210,10 +16235,10 @@
         <v>357</v>
       </c>
       <c r="C12" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D12" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E12" t="s">
         <v>126</v>
@@ -16234,7 +16259,7 @@
         <v>102.96</v>
       </c>
       <c r="L12" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -16248,10 +16273,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D13" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -16272,7 +16297,7 @@
         <v>57.59</v>
       </c>
       <c r="L13" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="M13">
         <v>291315</v>
@@ -16286,10 +16311,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D14" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E14" t="s">
         <v>126</v>
@@ -16310,7 +16335,7 @@
         <v>147.28</v>
       </c>
       <c r="L14" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -16321,13 +16346,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C15" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D15" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -16348,7 +16373,7 @@
         <v>102.01</v>
       </c>
       <c r="L15" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -16362,10 +16387,10 @@
         <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D16" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -16386,7 +16411,7 @@
         <v>56.91</v>
       </c>
       <c r="L16" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="M16">
         <v>387807</v>
@@ -16397,13 +16422,13 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C17" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D17" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -16424,7 +16449,7 @@
         <v>63.52</v>
       </c>
       <c r="L17" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -16438,10 +16463,10 @@
         <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D18" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -16462,7 +16487,7 @@
         <v>120.35</v>
       </c>
       <c r="L18" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -16476,10 +16501,10 @@
         <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D19" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -16500,7 +16525,7 @@
         <v>88.34</v>
       </c>
       <c r="L19" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -16514,10 +16539,10 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D20" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E20" t="s">
         <v>34</v>
@@ -16538,7 +16563,7 @@
         <v>46.99</v>
       </c>
       <c r="L20" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -16552,10 +16577,10 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D21" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -16576,7 +16601,7 @@
         <v>85.92</v>
       </c>
       <c r="L21" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="M21">
         <v>327260</v>
@@ -16590,10 +16615,10 @@
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D22" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -16614,7 +16639,7 @@
         <v>83.02</v>
       </c>
       <c r="L22" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -16628,10 +16653,10 @@
         <v>431</v>
       </c>
       <c r="C23" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D23" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -16652,7 +16677,7 @@
         <v>69.23</v>
       </c>
       <c r="L23" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -16663,13 +16688,13 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C24" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D24" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -16690,7 +16715,7 @@
         <v>59.83</v>
       </c>
       <c r="L24" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -16704,10 +16729,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D25" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -16728,7 +16753,7 @@
         <v>49.05</v>
       </c>
       <c r="L25" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="M25">
         <v>291662</v>
@@ -16742,10 +16767,10 @@
         <v>357</v>
       </c>
       <c r="C26" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D26" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E26" t="s">
         <v>126</v>
@@ -16766,7 +16791,7 @@
         <v>105.69</v>
       </c>
       <c r="L26" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -16780,10 +16805,10 @@
         <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D27" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E27" t="s">
         <v>152</v>
@@ -16804,7 +16829,7 @@
         <v>144.13</v>
       </c>
       <c r="L27" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -16818,10 +16843,10 @@
         <v>196</v>
       </c>
       <c r="C28" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D28" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -16842,7 +16867,7 @@
         <v>65.28</v>
       </c>
       <c r="L28" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -16856,10 +16881,10 @@
         <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D29" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -16880,7 +16905,7 @@
         <v>33.21</v>
       </c>
       <c r="L29" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -16894,10 +16919,10 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D30" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E30" t="s">
         <v>126</v>
@@ -16918,7 +16943,7 @@
         <v>63.89</v>
       </c>
       <c r="L30" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -16932,10 +16957,10 @@
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D31" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -16956,7 +16981,7 @@
         <v>95.34</v>
       </c>
       <c r="L31" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -16970,10 +16995,10 @@
         <v>260</v>
       </c>
       <c r="C32" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D32" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -16994,7 +17019,7 @@
         <v>46.47</v>
       </c>
       <c r="L32" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="M32">
         <v>371889</v>
@@ -17008,10 +17033,10 @@
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D33" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E33" t="s">
         <v>126</v>
@@ -17032,7 +17057,7 @@
         <v>105.39</v>
       </c>
       <c r="L33" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -17043,13 +17068,13 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C34" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D34" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -17070,7 +17095,7 @@
         <v>68.569999999999993</v>
       </c>
       <c r="L34" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -17084,10 +17109,10 @@
         <v>357</v>
       </c>
       <c r="C35" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D35" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -17108,7 +17133,7 @@
         <v>67.84</v>
       </c>
       <c r="L35" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="M35">
         <v>327675</v>
@@ -17122,10 +17147,10 @@
         <v>357</v>
       </c>
       <c r="C36" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D36" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E36" t="s">
         <v>126</v>
@@ -17146,7 +17171,7 @@
         <v>112.34</v>
       </c>
       <c r="L36" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -17160,10 +17185,10 @@
         <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D37" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E37" t="s">
         <v>152</v>
@@ -17184,7 +17209,7 @@
         <v>112.71</v>
       </c>
       <c r="L37" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -17198,10 +17223,10 @@
         <v>331</v>
       </c>
       <c r="C38" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D38" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E38" t="s">
         <v>126</v>
@@ -17222,7 +17247,7 @@
         <v>76.069999999999993</v>
       </c>
       <c r="L38" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -17236,10 +17261,10 @@
         <v>406</v>
       </c>
       <c r="C39" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D39" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -17260,7 +17285,7 @@
         <v>66.89</v>
       </c>
       <c r="L39" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="M39">
         <v>352194</v>
@@ -17274,10 +17299,10 @@
         <v>326</v>
       </c>
       <c r="C40" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D40" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -17298,7 +17323,7 @@
         <v>35.93</v>
       </c>
       <c r="L40" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="M40">
         <v>352353</v>
@@ -17312,10 +17337,10 @@
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D41" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E41" t="s">
         <v>126</v>
@@ -17336,7 +17361,7 @@
         <v>47.57</v>
       </c>
       <c r="L41" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -17350,10 +17375,10 @@
         <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D42" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -17374,7 +17399,7 @@
         <v>87.53</v>
       </c>
       <c r="L42" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -17388,10 +17413,10 @@
         <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D43" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -17412,7 +17437,7 @@
         <v>66.44</v>
       </c>
       <c r="L43" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -17426,10 +17451,10 @@
         <v>326</v>
       </c>
       <c r="C44" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D44" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -17450,7 +17475,7 @@
         <v>47.66</v>
       </c>
       <c r="L44" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="M44">
         <v>389572</v>
@@ -17461,13 +17486,13 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C45" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D45" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -17488,7 +17513,7 @@
         <v>68.97</v>
       </c>
       <c r="L45" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -17499,13 +17524,13 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C46" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D46" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -17526,7 +17551,7 @@
         <v>59.27</v>
       </c>
       <c r="L46" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -17540,10 +17565,10 @@
         <v>288</v>
       </c>
       <c r="C47" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D47" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -17564,7 +17589,7 @@
         <v>92.75</v>
       </c>
       <c r="L47" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="M47">
         <v>300087</v>
@@ -17578,10 +17603,10 @@
         <v>326</v>
       </c>
       <c r="C48" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D48" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -17602,7 +17627,7 @@
         <v>43.55</v>
       </c>
       <c r="L48" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -17616,10 +17641,10 @@
         <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D49" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -17640,7 +17665,7 @@
         <v>49.51</v>
       </c>
       <c r="L49" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -17651,13 +17676,13 @@
         <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C50" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D50" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -17678,7 +17703,7 @@
         <v>131.66</v>
       </c>
       <c r="L50" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -17692,10 +17717,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D51" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -17716,7 +17741,7 @@
         <v>85.54</v>
       </c>
       <c r="L51" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="M51">
         <v>328220</v>
@@ -17730,10 +17755,10 @@
         <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D52" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -17754,7 +17779,7 @@
         <v>77.78</v>
       </c>
       <c r="L52" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="M52">
         <v>392155</v>
@@ -17768,10 +17793,10 @@
         <v>357</v>
       </c>
       <c r="C53" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D53" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E53" t="s">
         <v>126</v>
@@ -17792,7 +17817,7 @@
         <v>60.9</v>
       </c>
       <c r="L53" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="M53">
         <v>292487</v>
@@ -17806,10 +17831,10 @@
         <v>357</v>
       </c>
       <c r="C54" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D54" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E54" t="s">
         <v>126</v>
@@ -17830,7 +17855,7 @@
         <v>109.85</v>
       </c>
       <c r="L54" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -17844,10 +17869,10 @@
         <v>45</v>
       </c>
       <c r="C55" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D55" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E55" t="s">
         <v>152</v>
@@ -17868,7 +17893,7 @@
         <v>94.66</v>
       </c>
       <c r="L55" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -17881,8 +17906,16 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -17933,10 +17966,10 @@
         <v>438</v>
       </c>
       <c r="C2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -17951,7 +17984,7 @@
         <v>111.24</v>
       </c>
       <c r="L2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -17962,13 +17995,13 @@
         <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C3" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D3" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -17983,7 +18016,7 @@
         <v>50</v>
       </c>
       <c r="L3" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -17997,10 +18030,10 @@
         <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -18015,7 +18048,7 @@
         <v>45.64</v>
       </c>
       <c r="L4" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -18029,10 +18062,10 @@
         <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -18047,7 +18080,7 @@
         <v>30.09</v>
       </c>
       <c r="L5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -18061,10 +18094,10 @@
         <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D6" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
@@ -18079,7 +18112,7 @@
         <v>42.26</v>
       </c>
       <c r="L6" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -18093,10 +18126,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D7" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -18111,7 +18144,7 @@
         <v>56.34</v>
       </c>
       <c r="L7" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -18125,10 +18158,10 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D8" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -18143,41 +18176,41 @@
         <v>69.88</v>
       </c>
       <c r="L8" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>913</v>
-      </c>
-      <c r="C9" t="s">
-        <v>914</v>
-      </c>
-      <c r="D9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
+      <c r="B9" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
         <v>285.55700000000002</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>1.31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>374.08</v>
       </c>
-      <c r="L9" t="s">
-        <v>916</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="M9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18189,10 +18222,10 @@
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D10" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
@@ -18207,7 +18240,7 @@
         <v>10.58</v>
       </c>
       <c r="L10" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -18218,13 +18251,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C11" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D11" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
@@ -18239,7 +18272,7 @@
         <v>61.22</v>
       </c>
       <c r="L11" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -18250,13 +18283,13 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C12" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D12" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>
@@ -18271,7 +18304,7 @@
         <v>25.5</v>
       </c>
       <c r="L12" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -18282,13 +18315,13 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C13" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="D13" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E13" t="s">
         <v>126</v>
@@ -18303,7 +18336,7 @@
         <v>90.12</v>
       </c>
       <c r="L13" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -18314,62 +18347,62 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>438</v>
       </c>
       <c r="C14" t="s">
-        <v>925</v>
+        <v>901</v>
       </c>
       <c r="D14" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>590</v>
       </c>
       <c r="F14">
-        <v>135</v>
+        <v>21.283000000000001</v>
       </c>
       <c r="J14">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="K14">
-        <v>175.5</v>
+        <v>12.77</v>
       </c>
       <c r="L14" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M14">
-        <v>195014</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C15" t="s">
-        <v>898</v>
-      </c>
-      <c r="D15" t="s">
-        <v>899</v>
-      </c>
-      <c r="E15" t="s">
-        <v>587</v>
-      </c>
-      <c r="F15">
-        <v>21.283000000000001</v>
-      </c>
-      <c r="J15">
-        <v>0.6</v>
-      </c>
-      <c r="K15">
-        <v>12.77</v>
-      </c>
-      <c r="L15" t="s">
-        <v>928</v>
-      </c>
-      <c r="M15">
+      <c r="B15" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1">
+        <v>220.12200000000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="K15" s="1">
+        <v>288.36</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="M15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18378,94 +18411,94 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>913</v>
+        <v>357</v>
       </c>
       <c r="C16" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D16" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
       </c>
       <c r="F16">
-        <v>220.12200000000001</v>
+        <v>34.459000000000003</v>
       </c>
       <c r="J16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="K16">
-        <v>288.36</v>
+        <v>45.83</v>
       </c>
       <c r="L16" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>357</v>
-      </c>
-      <c r="C17" t="s">
-        <v>932</v>
-      </c>
-      <c r="D17" t="s">
-        <v>933</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17">
-        <v>34.459000000000003</v>
-      </c>
-      <c r="J17">
+    <row r="17" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>7.41</v>
+      </c>
+      <c r="K17" s="1">
+        <v>14.82</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1">
+        <v>200.00800000000001</v>
+      </c>
+      <c r="J18" s="1">
         <v>1.33</v>
       </c>
-      <c r="K17">
-        <v>45.83</v>
-      </c>
-      <c r="L17" t="s">
-        <v>934</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>331</v>
-      </c>
-      <c r="C18" t="s">
-        <v>935</v>
-      </c>
-      <c r="D18" t="s">
-        <v>936</v>
-      </c>
-      <c r="E18" t="s">
-        <v>937</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="J18">
-        <v>7.41</v>
-      </c>
-      <c r="K18">
-        <v>14.82</v>
-      </c>
-      <c r="L18" t="s">
-        <v>938</v>
-      </c>
-      <c r="M18">
+      <c r="K18" s="1">
+        <v>266.01</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="M18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18474,62 +18507,62 @@
         <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="D19" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19">
-        <v>200.00800000000001</v>
+        <v>22.827000000000002</v>
       </c>
       <c r="J19">
         <v>1.33</v>
       </c>
       <c r="K19">
-        <v>266.01</v>
+        <v>30.36</v>
       </c>
       <c r="L19" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" t="s">
-        <v>940</v>
-      </c>
-      <c r="D20" t="s">
-        <v>941</v>
-      </c>
-      <c r="E20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20">
-        <v>22.827000000000002</v>
-      </c>
-      <c r="J20">
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1">
+        <v>207</v>
+      </c>
+      <c r="J20" s="1">
         <v>1.33</v>
       </c>
-      <c r="K20">
-        <v>30.36</v>
-      </c>
-      <c r="L20" t="s">
-        <v>942</v>
-      </c>
-      <c r="M20">
+      <c r="K20" s="1">
+        <v>275.31</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="M20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18538,28 +18571,28 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D21" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
       </c>
       <c r="F21">
-        <v>207</v>
+        <v>80.94</v>
       </c>
       <c r="J21">
         <v>1.33</v>
       </c>
       <c r="K21">
-        <v>275.31</v>
+        <v>107.65</v>
       </c>
       <c r="L21" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -18570,62 +18603,62 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D22" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
       </c>
       <c r="F22">
-        <v>80.94</v>
+        <v>53.811999999999998</v>
       </c>
       <c r="J22">
         <v>1.33</v>
       </c>
       <c r="K22">
-        <v>107.65</v>
+        <v>71.569999999999993</v>
       </c>
       <c r="L22" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>949</v>
-      </c>
-      <c r="D23" t="s">
-        <v>950</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23">
-        <v>53.811999999999998</v>
-      </c>
-      <c r="J23">
-        <v>1.33</v>
-      </c>
-      <c r="K23">
-        <v>71.569999999999993</v>
-      </c>
-      <c r="L23" t="s">
-        <v>951</v>
-      </c>
-      <c r="M23">
+      <c r="B23" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1">
+        <v>375</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="K23" s="1">
+        <v>510</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="M23" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18634,94 +18667,94 @@
         <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>952</v>
+        <v>249</v>
       </c>
       <c r="C24" t="s">
-        <v>953</v>
+        <v>913</v>
       </c>
       <c r="D24" t="s">
-        <v>954</v>
+        <v>914</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F24">
-        <v>375</v>
+        <v>50.328000000000003</v>
       </c>
       <c r="J24">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="K24">
-        <v>510</v>
+        <v>64.42</v>
       </c>
       <c r="L24" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>249</v>
-      </c>
-      <c r="C25" t="s">
-        <v>910</v>
-      </c>
-      <c r="D25" t="s">
-        <v>911</v>
-      </c>
-      <c r="E25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25">
-        <v>50.328000000000003</v>
-      </c>
-      <c r="J25">
-        <v>1.28</v>
-      </c>
-      <c r="K25">
-        <v>64.42</v>
-      </c>
-      <c r="L25" t="s">
-        <v>956</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="25" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B26" t="s">
-        <v>913</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B25" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D25" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26">
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1">
         <v>170</v>
       </c>
-      <c r="J26">
+      <c r="J25" s="1">
         <v>1.35</v>
       </c>
-      <c r="K26">
+      <c r="K25" s="1">
         <v>229.5</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L25" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="M26">
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1">
+        <v>244.57</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="K26" s="1">
+        <v>330.17</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="M26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18730,28 +18763,28 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>913</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>914</v>
+        <v>959</v>
       </c>
       <c r="D27" t="s">
-        <v>915</v>
+        <v>960</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
       </c>
       <c r="F27">
-        <v>244.57</v>
+        <v>182</v>
       </c>
       <c r="J27">
         <v>1.35</v>
       </c>
       <c r="K27">
-        <v>330.17</v>
+        <v>245.7</v>
       </c>
       <c r="L27" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -18759,31 +18792,31 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>959</v>
+        <v>906</v>
       </c>
       <c r="D28" t="s">
-        <v>960</v>
+        <v>907</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F28">
-        <v>182</v>
+        <v>17.402999999999999</v>
       </c>
       <c r="J28">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="K28">
-        <v>245.7</v>
+        <v>23.32</v>
       </c>
       <c r="L28" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -18794,28 +18827,28 @@
         <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>903</v>
+        <v>946</v>
       </c>
       <c r="D29" t="s">
-        <v>904</v>
+        <v>947</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>17.402999999999999</v>
+        <v>49.427999999999997</v>
       </c>
       <c r="J29">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K29">
-        <v>23.32</v>
+        <v>68.209999999999994</v>
       </c>
       <c r="L29" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -18826,156 +18859,156 @@
         <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="D30" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
       </c>
       <c r="F30">
-        <v>49.427999999999997</v>
+        <v>21.457000000000001</v>
       </c>
       <c r="J30">
         <v>1.38</v>
       </c>
       <c r="K30">
-        <v>68.209999999999994</v>
+        <v>29.61</v>
       </c>
       <c r="L30" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>932</v>
-      </c>
-      <c r="D31" t="s">
-        <v>933</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31">
-        <v>21.457000000000001</v>
-      </c>
-      <c r="J31">
+      <c r="B31" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="1">
+        <v>284.971</v>
+      </c>
+      <c r="J31" s="1">
         <v>1.38</v>
       </c>
-      <c r="K31">
-        <v>29.61</v>
-      </c>
-      <c r="L31" t="s">
-        <v>964</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="K31" s="1">
+        <v>393.26</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
-        <v>913</v>
-      </c>
-      <c r="C32" t="s">
-        <v>929</v>
-      </c>
-      <c r="D32" t="s">
-        <v>930</v>
-      </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32">
-        <v>284.971</v>
-      </c>
-      <c r="J32">
+      <c r="B32" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1">
+        <v>310</v>
+      </c>
+      <c r="J32" s="1">
         <v>1.38</v>
       </c>
-      <c r="K32">
-        <v>393.26</v>
-      </c>
-      <c r="L32" t="s">
-        <v>965</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="K32" s="1">
+        <v>427.8</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B33" t="s">
-        <v>913</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="E33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33">
-        <v>310</v>
-      </c>
-      <c r="J33">
-        <v>1.38</v>
-      </c>
-      <c r="K33">
-        <v>427.8</v>
-      </c>
-      <c r="L33" t="s">
-        <v>966</v>
-      </c>
-      <c r="M33">
+      <c r="E33" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="F33" s="1">
+        <v>37.451000000000001</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="K33" s="1">
+        <v>45.69</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="M33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
+        <v>834</v>
+      </c>
+      <c r="C34" t="s">
         <v>913</v>
       </c>
-      <c r="C34" t="s">
-        <v>953</v>
-      </c>
       <c r="D34" t="s">
-        <v>954</v>
+        <v>914</v>
       </c>
       <c r="E34" t="s">
-        <v>967</v>
+        <v>34</v>
       </c>
       <c r="F34">
-        <v>37.451000000000001</v>
+        <v>31.677</v>
       </c>
       <c r="J34">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="K34">
-        <v>45.69</v>
+        <v>41.18</v>
       </c>
       <c r="L34" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -18986,28 +19019,28 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>831</v>
+        <v>438</v>
       </c>
       <c r="C35" t="s">
-        <v>910</v>
+        <v>970</v>
       </c>
       <c r="D35" t="s">
-        <v>911</v>
+        <v>971</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F35">
-        <v>31.677</v>
+        <v>37.482999999999997</v>
       </c>
       <c r="J35">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="K35">
-        <v>41.18</v>
+        <v>53.6</v>
       </c>
       <c r="L35" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -19015,31 +19048,31 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>438</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="D36" t="s">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>590</v>
       </c>
       <c r="F36">
-        <v>37.482999999999997</v>
+        <v>39.031999999999996</v>
       </c>
       <c r="J36">
-        <v>1.43</v>
+        <v>0.62</v>
       </c>
       <c r="K36">
-        <v>53.6</v>
+        <v>24.2</v>
       </c>
       <c r="L36" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -19050,28 +19083,28 @@
         <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>326</v>
       </c>
       <c r="C37" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="D37" t="s">
-        <v>923</v>
+        <v>902</v>
       </c>
       <c r="E37" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F37">
-        <v>39.031999999999996</v>
+        <v>17.984000000000002</v>
       </c>
       <c r="J37">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="K37">
-        <v>24.2</v>
+        <v>10.97</v>
       </c>
       <c r="L37" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -19082,28 +19115,28 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>326</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="D38" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="E38" t="s">
-        <v>587</v>
+        <v>34</v>
       </c>
       <c r="F38">
-        <v>17.984000000000002</v>
+        <v>34.433</v>
       </c>
       <c r="J38">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="K38">
-        <v>10.97</v>
+        <v>46.14</v>
       </c>
       <c r="L38" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -19111,31 +19144,31 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>910</v>
+        <v>959</v>
       </c>
       <c r="D39" t="s">
-        <v>911</v>
+        <v>960</v>
       </c>
       <c r="E39" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F39">
-        <v>34.433</v>
+        <v>238.00700000000001</v>
       </c>
       <c r="J39">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="K39">
-        <v>46.14</v>
+        <v>340.35</v>
       </c>
       <c r="L39" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -19146,28 +19179,28 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>900</v>
       </c>
       <c r="C40" t="s">
-        <v>959</v>
+        <v>901</v>
       </c>
       <c r="D40" t="s">
-        <v>960</v>
+        <v>902</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F40">
-        <v>238.00700000000001</v>
+        <v>10.568</v>
       </c>
       <c r="J40">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="K40">
-        <v>340.35</v>
+        <v>13.95</v>
       </c>
       <c r="L40" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -19178,94 +19211,94 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>897</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>898</v>
+        <v>978</v>
       </c>
       <c r="D41" t="s">
-        <v>899</v>
+        <v>979</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>10.568</v>
+        <v>66.662000000000006</v>
       </c>
       <c r="J41">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="K41">
-        <v>13.95</v>
+        <v>96.66</v>
       </c>
       <c r="L41" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" t="s">
-        <v>978</v>
-      </c>
-      <c r="D42" t="s">
-        <v>979</v>
-      </c>
-      <c r="E42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42">
-        <v>66.662000000000006</v>
-      </c>
-      <c r="J42">
-        <v>1.45</v>
-      </c>
-      <c r="K42">
-        <v>96.66</v>
-      </c>
-      <c r="L42" t="s">
-        <v>980</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B42" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="1">
+        <v>225</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="K42" s="1">
+        <v>321.75</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B43" t="s">
-        <v>913</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="E43" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43">
-        <v>225</v>
-      </c>
-      <c r="J43">
-        <v>1.43</v>
-      </c>
-      <c r="K43">
-        <v>321.75</v>
-      </c>
-      <c r="L43" t="s">
-        <v>981</v>
-      </c>
-      <c r="M43">
+      <c r="E43" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="F43" s="1">
+        <v>18.27</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="K43" s="1">
+        <v>22.29</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="M43" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19274,28 +19307,28 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="C44" t="s">
-        <v>953</v>
+        <v>901</v>
       </c>
       <c r="D44" t="s">
-        <v>954</v>
+        <v>902</v>
       </c>
       <c r="E44" t="s">
-        <v>967</v>
+        <v>590</v>
       </c>
       <c r="F44">
-        <v>18.27</v>
+        <v>14.279</v>
       </c>
       <c r="J44">
-        <v>1.22</v>
+        <v>0.61</v>
       </c>
       <c r="K44">
-        <v>22.29</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="L44" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -19306,62 +19339,62 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C45" t="s">
-        <v>898</v>
+        <v>984</v>
       </c>
       <c r="D45" t="s">
-        <v>899</v>
+        <v>985</v>
       </c>
       <c r="E45" t="s">
-        <v>587</v>
+        <v>34</v>
       </c>
       <c r="F45">
-        <v>14.279</v>
+        <v>32.347999999999999</v>
       </c>
       <c r="J45">
-        <v>0.61</v>
+        <v>1.32</v>
       </c>
       <c r="K45">
-        <v>8.7100000000000009</v>
+        <v>42.7</v>
       </c>
       <c r="L45" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B46" t="s">
-        <v>918</v>
-      </c>
-      <c r="C46" t="s">
-        <v>984</v>
-      </c>
-      <c r="D46" t="s">
-        <v>985</v>
-      </c>
-      <c r="E46" t="s">
-        <v>34</v>
-      </c>
-      <c r="F46">
-        <v>32.347999999999999</v>
-      </c>
-      <c r="J46">
-        <v>1.32</v>
-      </c>
-      <c r="K46">
-        <v>42.7</v>
-      </c>
-      <c r="L46" t="s">
-        <v>986</v>
-      </c>
-      <c r="M46">
+      <c r="B46" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1">
+        <v>200.09800000000001</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="K46" s="1">
+        <v>286.14</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="M46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19370,28 +19403,28 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>987</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="D47" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
       </c>
       <c r="F47">
-        <v>200.09800000000001</v>
+        <v>46.378</v>
       </c>
       <c r="J47">
         <v>1.43</v>
       </c>
       <c r="K47">
-        <v>286.14</v>
+        <v>66.319999999999993</v>
       </c>
       <c r="L47" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -19399,31 +19432,31 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="D48" t="s">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
       </c>
       <c r="F48">
-        <v>46.378</v>
+        <v>209</v>
       </c>
       <c r="J48">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="K48">
-        <v>66.319999999999993</v>
+        <v>303.05</v>
       </c>
       <c r="L48" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -19434,28 +19467,28 @@
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>959</v>
+        <v>913</v>
       </c>
       <c r="D49" t="s">
-        <v>960</v>
+        <v>914</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F49">
-        <v>209</v>
+        <v>21.187000000000001</v>
       </c>
       <c r="J49">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="K49">
-        <v>303.05</v>
+        <v>28.39</v>
       </c>
       <c r="L49" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -19466,28 +19499,28 @@
         <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>357</v>
       </c>
       <c r="C50" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="D50" t="s">
-        <v>911</v>
+        <v>933</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F50">
-        <v>21.187000000000001</v>
+        <v>49</v>
       </c>
       <c r="J50">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="K50">
-        <v>28.39</v>
+        <v>71.540000000000006</v>
       </c>
       <c r="L50" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -19495,31 +19528,31 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>357</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="D51" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
       </c>
       <c r="F51">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="J51">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="K51">
-        <v>71.540000000000006</v>
+        <v>241.08</v>
       </c>
       <c r="L51" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -19530,28 +19563,28 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>959</v>
+        <v>994</v>
       </c>
       <c r="D52" t="s">
-        <v>960</v>
+        <v>995</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
       </c>
       <c r="F52">
-        <v>164</v>
+        <v>25.516999999999999</v>
       </c>
       <c r="J52">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="K52">
-        <v>241.08</v>
+        <v>37</v>
       </c>
       <c r="L52" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -19562,62 +19595,62 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>363</v>
       </c>
       <c r="C53" t="s">
-        <v>994</v>
+        <v>940</v>
       </c>
       <c r="D53" t="s">
-        <v>995</v>
+        <v>941</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
       </c>
       <c r="F53">
-        <v>25.516999999999999</v>
+        <v>32.823</v>
       </c>
       <c r="J53">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="K53">
-        <v>37</v>
+        <v>48.25</v>
       </c>
       <c r="L53" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B54" t="s">
-        <v>363</v>
-      </c>
-      <c r="C54" t="s">
-        <v>940</v>
-      </c>
-      <c r="D54" t="s">
-        <v>941</v>
-      </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54">
-        <v>32.823</v>
-      </c>
-      <c r="J54">
-        <v>1.47</v>
-      </c>
-      <c r="K54">
-        <v>48.25</v>
-      </c>
-      <c r="L54" t="s">
-        <v>997</v>
-      </c>
-      <c r="M54">
+      <c r="B54" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="1">
+        <v>200.02699999999999</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="K54" s="1">
+        <v>292.04000000000002</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="M54" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19626,63 +19659,63 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>640</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>929</v>
+        <v>999</v>
       </c>
       <c r="D55" t="s">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F55">
-        <v>200.02699999999999</v>
+        <v>65.691999999999993</v>
       </c>
       <c r="J55">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="K55">
-        <v>292.04000000000002</v>
+        <v>112.99</v>
       </c>
       <c r="L55" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>15350</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>438</v>
       </c>
       <c r="C56" t="s">
-        <v>999</v>
+        <v>913</v>
       </c>
       <c r="D56" t="s">
-        <v>1000</v>
+        <v>914</v>
       </c>
       <c r="E56" t="s">
-        <v>126</v>
+        <v>590</v>
       </c>
       <c r="F56">
-        <v>65.691999999999993</v>
+        <v>24.21</v>
       </c>
       <c r="J56">
-        <v>1.72</v>
+        <v>0.62</v>
       </c>
       <c r="K56">
-        <v>112.99</v>
+        <v>15.01</v>
       </c>
       <c r="L56" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M56">
-        <v>15350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -19690,28 +19723,28 @@
         <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>438</v>
+        <v>196</v>
       </c>
       <c r="C57" t="s">
-        <v>910</v>
+        <v>959</v>
       </c>
       <c r="D57" t="s">
-        <v>911</v>
+        <v>960</v>
       </c>
       <c r="E57" t="s">
-        <v>587</v>
+        <v>17</v>
       </c>
       <c r="F57">
-        <v>24.21</v>
+        <v>183.16900000000001</v>
       </c>
       <c r="J57">
-        <v>0.62</v>
+        <v>1.48</v>
       </c>
       <c r="K57">
-        <v>15.01</v>
+        <v>271.08999999999997</v>
       </c>
       <c r="L57" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -19722,28 +19755,28 @@
         <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C58" t="s">
-        <v>959</v>
+        <v>932</v>
       </c>
       <c r="D58" t="s">
-        <v>960</v>
+        <v>933</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F58">
-        <v>183.16900000000001</v>
+        <v>40.479999999999997</v>
       </c>
       <c r="J58">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="K58">
-        <v>271.08999999999997</v>
+        <v>69.22</v>
       </c>
       <c r="L58" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -19754,28 +19787,28 @@
         <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>217</v>
+        <v>916</v>
       </c>
       <c r="C59" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="D59" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F59">
-        <v>40.479999999999997</v>
+        <v>76.281999999999996</v>
       </c>
       <c r="J59">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="K59">
-        <v>69.22</v>
+        <v>113.66</v>
       </c>
       <c r="L59" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -19783,65 +19816,65 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s">
-        <v>913</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>959</v>
+        <v>906</v>
       </c>
       <c r="D60" t="s">
-        <v>960</v>
+        <v>907</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F60">
-        <v>76.281999999999996</v>
+        <v>17.698</v>
       </c>
       <c r="J60">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="K60">
-        <v>113.66</v>
+        <v>24.6</v>
       </c>
       <c r="L60" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B61" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>903</v>
-      </c>
-      <c r="D61" t="s">
-        <v>904</v>
-      </c>
-      <c r="E61" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61">
-        <v>17.698</v>
-      </c>
-      <c r="J61">
-        <v>1.39</v>
-      </c>
-      <c r="K61">
-        <v>24.6</v>
-      </c>
-      <c r="L61" t="s">
-        <v>1006</v>
-      </c>
-      <c r="M61">
+      <c r="B61" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="1">
+        <v>225</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>337.5</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="M61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19850,28 +19883,28 @@
         <v>317</v>
       </c>
       <c r="B62" t="s">
-        <v>913</v>
+        <v>326</v>
       </c>
       <c r="C62" t="s">
-        <v>953</v>
+        <v>906</v>
       </c>
       <c r="D62" t="s">
-        <v>954</v>
+        <v>907</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F62">
-        <v>225</v>
+        <v>17.741</v>
       </c>
       <c r="J62">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="K62">
-        <v>337.5</v>
+        <v>24.66</v>
       </c>
       <c r="L62" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -19879,31 +19912,31 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>317</v>
+        <v>191</v>
       </c>
       <c r="B63" t="s">
-        <v>326</v>
+        <v>575</v>
       </c>
       <c r="C63" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D63" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E63" t="s">
         <v>34</v>
       </c>
       <c r="F63">
-        <v>17.741</v>
+        <v>51.829000000000001</v>
       </c>
       <c r="J63">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="K63">
-        <v>24.66</v>
+        <v>72.56</v>
       </c>
       <c r="L63" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -19914,28 +19947,28 @@
         <v>191</v>
       </c>
       <c r="B64" t="s">
-        <v>572</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="D64" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="E64" t="s">
         <v>34</v>
       </c>
       <c r="F64">
-        <v>51.829000000000001</v>
+        <v>21.504000000000001</v>
       </c>
       <c r="J64">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="K64">
-        <v>72.56</v>
+        <v>29.46</v>
       </c>
       <c r="L64" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M64">
         <v>0</v>
@@ -19946,62 +19979,30 @@
         <v>191</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>575</v>
       </c>
       <c r="C65" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D65" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E65" t="s">
         <v>34</v>
       </c>
       <c r="F65">
-        <v>21.504000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="J65">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="K65">
-        <v>29.46</v>
+        <v>31.5</v>
       </c>
       <c r="L65" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>191</v>
-      </c>
-      <c r="B66" t="s">
-        <v>572</v>
-      </c>
-      <c r="C66" t="s">
-        <v>903</v>
-      </c>
-      <c r="D66" t="s">
-        <v>904</v>
-      </c>
-      <c r="E66" t="s">
-        <v>34</v>
-      </c>
-      <c r="F66">
-        <v>22.5</v>
-      </c>
-      <c r="J66">
-        <v>1.4</v>
-      </c>
-      <c r="K66">
-        <v>31.5</v>
-      </c>
-      <c r="L66" t="s">
-        <v>1011</v>
-      </c>
-      <c r="M66">
         <v>0</v>
       </c>
     </row>

--- a/result/eko_transactions.xlsx
+++ b/result/eko_transactions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0AD251-DA96-45D9-A0D8-B887541015E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF6A1BC-685F-4B83-88CD-632F29A81719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="35" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3132,8 +3132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20290,7 +20291,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -20303,7 +20304,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -20344,7 +20345,7 @@
       <c r="C2" t="s">
         <v>1008</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>1009</v>
       </c>
       <c r="E2" t="s">
@@ -20376,7 +20377,7 @@
       <c r="C3" t="s">
         <v>1008</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>1009</v>
       </c>
       <c r="E3" t="s">
